--- a/Claude_DEV_Training_20261012.xlsx
+++ b/Claude_DEV_Training_20261012.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Claude_Developer_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2DA44B-6E53-4FFB-96A4-6F1285A85B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96DC1B6-7912-410D-9ABF-80FBD4AEA42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28785" yWindow="-16305" windowWidth="29040" windowHeight="15720" tabRatio="883" xr2:uid="{8462B982-91BC-4A14-8263-FB54256DAF23}"/>
   </bookViews>

--- a/Claude_DEV_Training_20261012.xlsx
+++ b/Claude_DEV_Training_20261012.xlsx
@@ -8,32 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Claude_Developer_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96DC1B6-7912-410D-9ABF-80FBD4AEA42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4599EEA0-C45B-4539-9D10-E2C5574C040E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28785" yWindow="-16305" windowWidth="29040" windowHeight="15720" tabRatio="883" xr2:uid="{8462B982-91BC-4A14-8263-FB54256DAF23}"/>
+    <workbookView xWindow="2100" yWindow="3075" windowWidth="23235" windowHeight="10410" tabRatio="883" xr2:uid="{8462B982-91BC-4A14-8263-FB54256DAF23}"/>
   </bookViews>
   <sheets>
-    <sheet name="Agent Architecture" sheetId="1" r:id="rId1"/>
-    <sheet name="Agent Construction with Claude" sheetId="2" r:id="rId2"/>
-    <sheet name="Agent Patterns and Frameworks" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Claude API Mechanics" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
-    <sheet name="Sheet10" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet11" sheetId="11" r:id="rId11"/>
-    <sheet name="Sheet12" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet13" sheetId="13" r:id="rId13"/>
-    <sheet name="Sheet14" sheetId="14" r:id="rId14"/>
-    <sheet name="Sheet15" sheetId="15" r:id="rId15"/>
-    <sheet name="Sheet16" sheetId="16" r:id="rId16"/>
-    <sheet name="Sheet17" sheetId="17" r:id="rId17"/>
-    <sheet name="Sheet18" sheetId="18" r:id="rId18"/>
-    <sheet name="Sheet19" sheetId="19" r:id="rId19"/>
-    <sheet name="Sheet20" sheetId="20" r:id="rId20"/>
-    <sheet name="Sheet21" sheetId="21" r:id="rId21"/>
+    <sheet name="Definitions" sheetId="22" r:id="rId1"/>
+    <sheet name="ALL_TOPICS" sheetId="23" r:id="rId2"/>
+    <sheet name="Agent Architecture" sheetId="1" r:id="rId3"/>
+    <sheet name="Agent Construction with Claude" sheetId="2" r:id="rId4"/>
+    <sheet name="Agent Patterns and Frameworks" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId7"/>
+    <sheet name="Claude API Mechanics" sheetId="6" r:id="rId8"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId9"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId10"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId11"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId12"/>
+    <sheet name="Sheet11" sheetId="11" r:id="rId13"/>
+    <sheet name="Sheet12" sheetId="12" r:id="rId14"/>
+    <sheet name="Sheet13" sheetId="13" r:id="rId15"/>
+    <sheet name="Sheet14" sheetId="14" r:id="rId16"/>
+    <sheet name="Sheet15" sheetId="15" r:id="rId17"/>
+    <sheet name="Sheet16" sheetId="16" r:id="rId18"/>
+    <sheet name="Sheet17" sheetId="17" r:id="rId19"/>
+    <sheet name="Sheet18" sheetId="18" r:id="rId20"/>
+    <sheet name="Sheet19" sheetId="19" r:id="rId21"/>
+    <sheet name="Sheet20" sheetId="20" r:id="rId22"/>
+    <sheet name="Sheet21" sheetId="21" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="131">
   <si>
     <t>Domain 1: Agents and Workflows (14.7%)</t>
   </si>
@@ -2034,13 +2036,293 @@
   </si>
   <si>
     <t>https://www.timolabs.dev/certifications/developer-foundations#study-guide</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Claude Console</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Session</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Abbr.</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Agents</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Hooks</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>MCP Servers</t>
+  </si>
+  <si>
+    <t>Connect to data sources, websites</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Hook</t>
+  </si>
+  <si>
+    <t>MCP Server</t>
+  </si>
+  <si>
+    <t>Function Call to External Software</t>
+  </si>
+  <si>
+    <t>A Claude hook is a user-defined automation that executes at a specific point in the Claude Code lifecycle. Developed by Anthropic for its command-line AI agent, hooks introduce a deterministic control layer. While standard AI prompts suggest how Claude should behave, hooks force strict rules that fire automatically whether the AI model cooperates or not.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A Claude skill is a reusable set of instructions, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>scripts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>, and resource files that teaches Claude how to perform a specialized task in a consistent, step-by-step way.</t>
+    </r>
+  </si>
+  <si>
+    <t>A Claude agent is an autonomous AI system powered by Anthropic's Claude models that plans, uses tools, takes multi-step actions (such as browsing the web, editing files, or running code), and checks its own work to achieve a goal with minimal human intervention.
+Unlike a standard chatbot that answers a single message at a time, an agent runs a continuous loop of plan -&gt; act -&gt; check -&gt; repeat.</t>
+  </si>
+  <si>
+    <t>A Claude session is an ongoing conversation, workspace, or active connection with Anthropic's Claude AI where context, history, and memory are retained.</t>
+  </si>
+  <si>
+    <t>A Claude Environment (or cloud environment) is an isolated, sandboxed runtime—typically running in a Linux container via gVisor or virtual machine infrastructure—where Claude executes code, runs terminal commands, and manages files safely away from local systems or core infrastructure</t>
+  </si>
+  <si>
+    <t>Domain 3: Claude Code (3.1%)</t>
+  </si>
+  <si>
+    <t>Claude Code Operation</t>
+  </si>
+  <si>
+    <t>Domain 4: Eval, Testing, and Debugging (2.6%)</t>
+  </si>
+  <si>
+    <t>Debugging and Error Handling</t>
+  </si>
+  <si>
+    <t>Domain 5: Model Selection and Optimization (16.8%)</t>
+  </si>
+  <si>
+    <t>LLM Fundamentals</t>
+  </si>
+  <si>
+    <t>Technical Fundamentals</t>
+  </si>
+  <si>
+    <t>Model Selection and Tradeoffs</t>
+  </si>
+  <si>
+    <t>Cost and Token Management</t>
+  </si>
+  <si>
+    <t>Domain 6: Prompt and Context Engineering (11.0%)</t>
+  </si>
+  <si>
+    <t>Context Engineering</t>
+  </si>
+  <si>
+    <t>Prompt Engineering</t>
+  </si>
+  <si>
+    <t>Output Handling</t>
+  </si>
+  <si>
+    <t>Domain 7: Security and Safety (8.1%)</t>
+  </si>
+  <si>
+    <t>AI Application Security</t>
+  </si>
+  <si>
+    <t>Guardrails and Safe Deployment</t>
+  </si>
+  <si>
+    <t>Claude Hooks</t>
+  </si>
+  <si>
+    <t>Identity, Secrets and Key Management</t>
+  </si>
+  <si>
+    <t>Domain 8: Tools and MCPs (10.6%)</t>
+  </si>
+  <si>
+    <t>Tool Implementation</t>
+  </si>
+  <si>
+    <t>MCP Server Development</t>
+  </si>
+  <si>
+    <t>Agentic Customization</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Chapters</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>https://code.claude.com/docs/en/sub-agents</t>
+  </si>
+  <si>
+    <t>"C:\dev\Claude_Developer_Training\.claude\agents\code-improver.md"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2154,8 +2436,27 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FF23251F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2174,8 +2475,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61CBF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2198,12 +2535,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2242,6 +2636,98 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2249,6 +2735,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2576,6 +3067,771 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506B35DF-08BF-4D98-9FC4-9107726A39A9}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="82.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>4</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>6</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C11" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C16" s="45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{080E15E6-EDEE-4171-8426-3B67B6A32587}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DD2813-4AE7-45F3-B170-ABCCD02C4212}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B679874E-9BB2-4AEF-B8A4-164D17AAFF6D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1E433C-7068-40F4-8550-E5AED6590CD8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA09248D-6B9E-4006-8491-9D05ADA80BFA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEDEFBCC-A769-493C-A691-D61C76F96B42}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612D3BD7-D87C-47B2-99D0-77F45D7B01A4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A866F452-46B8-4AC6-B933-3345C760B49A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365DE61-132C-45E5-86D9-ED2A87D37359}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2634BB17-3468-4BB2-A1BC-3D99C330EBCF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C13DE80-F81E-4D74-9132-951374DB0DC0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD7B290-01A3-4F81-8188-8DC0003C396D}">
+  <dimension ref="A1:C48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="33"/>
+    <col min="2" max="2" width="9.140625" style="19"/>
+    <col min="3" max="3" width="71.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="40">
+        <v>1</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="43">
+        <v>2</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="18">
+        <v>3</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="31"/>
+    </row>
+    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="29"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="18">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="18">
+        <v>5</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="18">
+        <v>6</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="18">
+        <v>7</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="18">
+        <v>8</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="18">
+        <v>9</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="32"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="31"/>
+    </row>
+    <row r="16" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="29"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="18">
+        <v>10</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="31"/>
+    </row>
+    <row r="20" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="29"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="18">
+        <v>11</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="31"/>
+    </row>
+    <row r="24" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="29"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="18">
+        <v>12</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="18">
+        <v>13</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="18">
+        <v>14</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="18">
+        <v>15</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="32"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="31"/>
+    </row>
+    <row r="31" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A31" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="38"/>
+      <c r="C31" s="36" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="29"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="18">
+        <v>16</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="18">
+        <v>17</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="18">
+        <v>18</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="32"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="31"/>
+    </row>
+    <row r="37" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A37" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="38"/>
+      <c r="C37" s="36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="29"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="18">
+        <v>19</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="18">
+        <v>20</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="18">
+        <v>21</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="18">
+        <v>22</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="32"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="31"/>
+    </row>
+    <row r="44" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A44" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="38"/>
+      <c r="C44" s="36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="29"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="18">
+        <v>23</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="18">
+        <v>24</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="18">
+        <v>25</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://www.timolabs.dev/certifications/developer-foundations/agent-architecture" xr:uid="{4E0651C1-9A09-4CB2-8BEA-7B6D6AC19C90}"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://www.timolabs.dev/certifications/developer-foundations/agent-construction" xr:uid="{AE1D5DE7-A663-4CD5-BE0D-C6BD49D855C0}"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://www.timolabs.dev/certifications/developer-foundations/agent-patterns-frameworks" xr:uid="{F5662827-FD7F-42A7-9664-AF8BF1F2499B}"/>
+    <hyperlink ref="C9" r:id="rId4" display="https://www.timolabs.dev/certifications/developer-foundations/understanding-requirements" xr:uid="{128C377A-ED8C-46B4-A8C1-653EEB7C0085}"/>
+    <hyperlink ref="C10" r:id="rId5" display="https://www.timolabs.dev/certifications/developer-foundations/systems-life-cycle" xr:uid="{640FCEDE-83F2-487B-A751-C5CE1DA00101}"/>
+    <hyperlink ref="C11" r:id="rId6" display="https://www.timolabs.dev/certifications/developer-foundations/claude-api-mechanics" xr:uid="{EC0ADD2C-E0C6-458A-8FF1-0EC0516AD195}"/>
+    <hyperlink ref="C12" r:id="rId7" display="https://www.timolabs.dev/certifications/developer-foundations/software-engineering-foundations" xr:uid="{01A72558-DD1A-4C98-935E-B43678EE5914}"/>
+    <hyperlink ref="C13" r:id="rId8" display="https://www.timolabs.dev/certifications/developer-foundations/claude-application-design" xr:uid="{C43D1DAF-F124-489A-A736-9E7F75E63CA5}"/>
+    <hyperlink ref="C14" r:id="rId9" display="https://www.timolabs.dev/certifications/developer-foundations/configuration-management" xr:uid="{82CB0761-2193-460E-B79E-23616EB7A292}"/>
+    <hyperlink ref="C18" r:id="rId10" display="https://www.timolabs.dev/certifications/developer-foundations/claude-code-operation" xr:uid="{ECAF2997-4E57-4282-BDEB-518B7410F503}"/>
+    <hyperlink ref="C22" r:id="rId11" display="https://www.timolabs.dev/certifications/developer-foundations/debugging-error-handling" xr:uid="{9688CA5A-B979-413B-804F-F0BEABE189A9}"/>
+    <hyperlink ref="C26" r:id="rId12" display="https://www.timolabs.dev/certifications/developer-foundations/llm-fundamentals" xr:uid="{FBD0A190-9833-4780-A4CD-51CD7D41FC18}"/>
+    <hyperlink ref="C27" r:id="rId13" display="https://www.timolabs.dev/certifications/developer-foundations/technical-fundamentals" xr:uid="{AC244295-C388-4B04-BB73-D20CBE70CF15}"/>
+    <hyperlink ref="C28" r:id="rId14" display="https://www.timolabs.dev/certifications/developer-foundations/model-selection-tradeoffs" xr:uid="{A0DA34C4-725F-4C15-9C54-BA5DC96F1BA9}"/>
+    <hyperlink ref="C29" r:id="rId15" display="https://www.timolabs.dev/certifications/developer-foundations/cost-token-management" xr:uid="{404DEA99-2325-41F7-A196-597CEF161D3E}"/>
+    <hyperlink ref="C33" r:id="rId16" display="https://www.timolabs.dev/certifications/developer-foundations/context-engineering" xr:uid="{7220C1B1-B4E6-43EE-B6C8-B68B3CB4B2BD}"/>
+    <hyperlink ref="C34" r:id="rId17" display="https://www.timolabs.dev/certifications/developer-foundations/prompt-engineering" xr:uid="{47EDE211-F4AF-4F68-B044-A0C88282A9D4}"/>
+    <hyperlink ref="C35" r:id="rId18" display="https://www.timolabs.dev/certifications/developer-foundations/output-handling" xr:uid="{08AE158E-1C4C-40C2-8474-9BF5A8035F77}"/>
+    <hyperlink ref="C39" r:id="rId19" display="https://www.timolabs.dev/certifications/developer-foundations/ai-application-security" xr:uid="{0C7FF1F7-B334-49B0-BB85-E800DDE2E0E8}"/>
+    <hyperlink ref="C40" r:id="rId20" display="https://www.timolabs.dev/certifications/developer-foundations/guardrails-safe-deployment" xr:uid="{A2684C36-FB81-4154-9647-B0D0C2F51E75}"/>
+    <hyperlink ref="C41" r:id="rId21" display="https://www.timolabs.dev/certifications/developer-foundations/claude-code-hooks" xr:uid="{08964464-FF42-4200-B59B-A95922B87BB0}"/>
+    <hyperlink ref="C42" r:id="rId22" display="https://www.timolabs.dev/certifications/developer-foundations/secrets-key-management" xr:uid="{CE2E386A-4047-4DEB-9F83-0DA3C8748A4B}"/>
+    <hyperlink ref="C46" r:id="rId23" display="https://www.timolabs.dev/certifications/developer-foundations/tool-implementation" xr:uid="{BDD88F78-DCA3-4886-AEB7-F0A8FCAB0E0F}"/>
+    <hyperlink ref="C47" r:id="rId24" display="https://www.timolabs.dev/certifications/developer-foundations/mcp-server-development" xr:uid="{A6A1693B-C04E-41BC-ADA5-FE295E61BAB4}"/>
+    <hyperlink ref="C48" r:id="rId25" display="https://www.timolabs.dev/certifications/developer-foundations/agentic-customization" xr:uid="{C307C25E-FB50-4FC4-8772-1C4859CE2F03}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4D8E60-8319-401B-961F-368177A9D74C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD0E800-B082-46E3-B6CC-12AF2A77751D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB259FB-508A-49AD-96B9-FF0B43735A70}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B982890D-BF03-4E67-8150-39866B7E036C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745E8B09-E6CF-440F-B0B2-2A2B333D6003}">
   <dimension ref="B1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2625,97 +3881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1E433C-7068-40F4-8550-E5AED6590CD8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA09248D-6B9E-4006-8491-9D05ADA80BFA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEDEFBCC-A769-493C-A691-D61C76F96B42}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612D3BD7-D87C-47B2-99D0-77F45D7B01A4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A866F452-46B8-4AC6-B933-3345C760B49A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365DE61-132C-45E5-86D9-ED2A87D37359}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2634BB17-3468-4BB2-A1BC-3D99C330EBCF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C13DE80-F81E-4D74-9132-951374DB0DC0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4D8E60-8319-401B-961F-368177A9D74C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD0E800-B082-46E3-B6CC-12AF2A77751D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E7415F-B973-4628-B57C-2A9542BB2A1D}">
   <dimension ref="B2:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2756,25 +3922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB259FB-508A-49AD-96B9-FF0B43735A70}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B982890D-BF03-4E67-8150-39866B7E036C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FB3777-C6DD-4B61-93BF-E8E84D1E1FFA}">
   <dimension ref="B2:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2815,7 +3963,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F691B03C-9291-462D-AC0B-D95BD691EB6E}">
   <dimension ref="B2:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2874,7 +4022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F008BEA3-042F-4293-BBE1-8ACBE1D34C5A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2883,7 +4031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317294ED-6CBA-4EB1-9088-416563297C76}">
   <dimension ref="B10:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3087,29 +4235,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7656BAE-492C-43B0-A3FB-EA423697F043}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DD2813-4AE7-45F3-B170-ABCCD02C4212}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B679874E-9BB2-4AEF-B8A4-164D17AAFF6D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>